--- a/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="58">
   <si>
     <t>Mat</t>
   </si>
@@ -82,7 +82,112 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>ROJAS</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JOSE ABRAHAM</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>ANGEL AMILCAR</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>CRISTAL</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>ELIEL</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
@@ -1010,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1042,25 +1147,324 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920311</v>
+        <v>20330051920025</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920026</v>
+      </c>
+      <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920029</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920031</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920034</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920035</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920037</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920340</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920345</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920365</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920301</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
         <v>14</v>
       </c>
-      <c r="G2">
-        <v>2</v>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920307</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920379</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920311</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="83">
   <si>
     <t>Mat</t>
   </si>
@@ -82,48 +82,93 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>NICIO</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>TZANAHUA</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>LASTRE</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
   </si>
   <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -133,22 +178,52 @@
     <t>YOPIHUA</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
     <t>BERISTAIN</t>
   </si>
   <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>ANGEL AMILCAR</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>ELIEL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
   </si>
   <si>
     <t>JOSE JULIAN</t>
@@ -163,31 +238,31 @@
     <t>OMAR</t>
   </si>
   <si>
-    <t>ANGEL AMILCAR</t>
-  </si>
-  <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
     <t>CRISTAL</t>
   </si>
   <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
+    <t>JOSSELIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>ATENEA</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>MONSERRATH YARETZY</t>
   </si>
   <si>
     <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ZULEICA RENATA</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
@@ -1115,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1147,16 +1222,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920025</v>
+        <v>20330051920362</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1170,16 +1245,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920026</v>
+        <v>20330051920034</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1193,16 +1268,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920029</v>
+        <v>20330051920035</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1216,22 +1291,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920031</v>
+        <v>20330051920340</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1239,22 +1314,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920034</v>
+        <v>20330051920345</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1262,22 +1337,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920035</v>
+        <v>20330051920044</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1285,22 +1360,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920037</v>
+        <v>20330051920301</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1308,22 +1383,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920340</v>
+        <v>20330051920307</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1331,22 +1406,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920345</v>
+        <v>20330051920379</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1354,116 +1429,323 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920365</v>
+        <v>20330051920025</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920301</v>
+        <v>20330051920026</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920307</v>
+        <v>20330051920029</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920379</v>
+        <v>20330051920031</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920311</v>
+        <v>20330051920037</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920221</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920233</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920237</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920241</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
         <v>57</v>
       </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="D19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920158</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920173</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920393</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920365</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920311</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
         <v>14</v>
       </c>
-      <c r="G15">
+      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="82">
   <si>
     <t>Mat</t>
   </si>
@@ -85,172 +85,169 @@
     <t>CORONA</t>
   </si>
   <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>LASTRE</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>LASTRE</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>JOSUE</t>
   </si>
   <si>
-    <t>ANGEL AMILCAR</t>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
   </si>
   <si>
     <t>MARCOS URIEL</t>
   </si>
   <si>
-    <t>CESAR</t>
+    <t>CRISTAL</t>
+  </si>
+  <si>
+    <t>JOSSELIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>ATENEA</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
   </si>
   <si>
     <t>ELIEL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ZULEICA RENATA</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JOSE ABRAHAM</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>JOSSELIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>ATENEA</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
   </si>
   <si>
     <t>DINA BERENICE</t>
@@ -689,7 +686,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -698,10 +695,10 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>83.78</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -861,16 +858,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>78.13</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -881,13 +881,13 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -907,16 +907,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>70.83</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -930,16 +933,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>69.44</v>
+      </c>
+      <c r="H5">
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -953,16 +959,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>72.73</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1041,16 +1050,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>65.63</v>
+        <v>78.13</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1061,7 +1070,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1070,10 +1079,10 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>83.78</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -1093,13 +1102,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>70.83</v>
       </c>
       <c r="H4">
         <v>6.8</v>
@@ -1119,16 +1128,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>69.44</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1231,7 +1240,7 @@
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1245,7 +1254,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920034</v>
+        <v>20330051920340</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1254,13 +1263,13 @@
         <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1268,7 +1277,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920035</v>
+        <v>20330051920354</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1277,13 +1286,13 @@
         <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1291,7 +1300,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920340</v>
+        <v>20330051920157</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1300,13 +1309,13 @@
         <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1314,7 +1323,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920345</v>
+        <v>20330051920388</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1323,13 +1332,13 @@
         <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1346,7 +1355,7 @@
         <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1360,16 +1369,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920301</v>
+        <v>20330051920285</v>
       </c>
       <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1383,16 +1392,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920307</v>
+        <v>20330051920301</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1406,16 +1415,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920379</v>
+        <v>20330051920307</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1429,39 +1438,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920025</v>
+        <v>20330051920379</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920026</v>
+        <v>20330051920025</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1475,16 +1484,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920029</v>
+        <v>20330051920035</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1498,16 +1507,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920031</v>
+        <v>20330051920037</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1521,22 +1530,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920037</v>
+        <v>20330051920221</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1544,16 +1553,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920221</v>
+        <v>20330051920233</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1567,16 +1576,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920233</v>
+        <v>20330051920237</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1590,16 +1599,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920237</v>
+        <v>20330051920241</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1613,22 +1622,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920241</v>
+        <v>20330051920345</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1645,7 +1654,7 @@
         <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1665,10 +1674,10 @@
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1688,10 +1697,10 @@
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1711,10 +1720,10 @@
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1737,7 +1746,7 @@
         <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="72">
   <si>
     <t>Mat</t>
   </si>
@@ -82,187 +82,157 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>CUEVAS</t>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
   </si>
   <si>
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
     <t>ARROYO</t>
   </si>
   <si>
-    <t>ZUÑIGA</t>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>LASTRE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>BERNARDO</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>LASTRE</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
   </si>
   <si>
     <t>CHONCOA</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>CESAR</t>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
   </si>
   <si>
     <t>JAHEL</t>
   </si>
   <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>MONSERRATH YARETZY</t>
+  </si>
+  <si>
+    <t>EVELYN IVETH</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>STEPHANIE</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>ATENEA</t>
+  </si>
+  <si>
+    <t>ELIEL</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
   </si>
   <si>
     <t>URIEL</t>
   </si>
   <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ZULEICA RENATA</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>JOSSELIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>ATENEA</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>MONSERRATH YARETZY</t>
-  </si>
-  <si>
     <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
   </si>
 </sst>
 </file>
@@ -884,16 +854,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88.89</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -985,16 +958,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>71.88</v>
+      </c>
+      <c r="H7">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1076,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1180,16 +1156,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>81.25</v>
+        <v>71.88</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1199,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1231,16 +1207,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920362</v>
+        <v>20330051920035</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1254,22 +1230,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920340</v>
+        <v>20330051920237</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1283,10 +1259,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1300,16 +1276,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920157</v>
+        <v>20330051920173</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1323,16 +1299,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920388</v>
+        <v>20330051920393</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1346,22 +1322,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920044</v>
+        <v>20330051920183</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1369,22 +1345,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920285</v>
+        <v>20330051920039</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1392,22 +1368,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920301</v>
+        <v>20330051920111</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1415,16 +1391,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920307</v>
+        <v>20330051920285</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1438,16 +1414,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920379</v>
+        <v>20330051920286</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1461,85 +1437,85 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920025</v>
+        <v>20330051920293</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
         <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920035</v>
+        <v>20330051920310</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920037</v>
+        <v>20330051920312</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920221</v>
+        <v>20330051920233</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1553,22 +1529,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920233</v>
+        <v>20330051920345</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1576,22 +1552,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920237</v>
+        <v>20330051920158</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1599,22 +1575,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920241</v>
+        <v>20330051920044</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1622,139 +1598,24 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920345</v>
+        <v>20330051920365</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920158</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920173</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920393</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920365</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920311</v>
-      </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="69">
   <si>
     <t>Mat</t>
   </si>
@@ -100,9 +100,6 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>VALENTE</t>
   </si>
   <si>
@@ -151,9 +148,6 @@
     <t>TEPEPA</t>
   </si>
   <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
     <t>GAMEZ</t>
   </si>
   <si>
@@ -197,9 +191,6 @@
   </si>
   <si>
     <t>EVELYN IVETH</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
   </si>
   <si>
     <t>ABIUD</t>
@@ -1175,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1213,10 +1204,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1236,10 +1227,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1259,10 +1250,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1282,10 +1273,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1308,7 +1299,7 @@
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1328,10 +1319,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1345,16 +1336,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920039</v>
+        <v>20330051920111</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1368,22 +1359,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920111</v>
+        <v>20330051920285</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1391,16 +1382,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920285</v>
+        <v>20330051920286</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1414,16 +1405,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920286</v>
+        <v>20330051920293</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1437,16 +1428,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920293</v>
+        <v>20330051920310</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1460,16 +1451,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920310</v>
+        <v>20330051920312</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1483,45 +1474,45 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920312</v>
+        <v>20330051920233</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920233</v>
+        <v>20330051920345</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1529,22 +1520,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920345</v>
+        <v>20330051920158</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1552,22 +1543,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920158</v>
+        <v>20330051920044</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1575,16 +1566,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920044</v>
+        <v>20330051920365</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1593,29 +1584,6 @@
         <v>13</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920365</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -82,148 +82,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
+    <t>ARROYO</t>
   </si>
   <si>
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>LASTRE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
   </si>
   <si>
     <t>VANNIA GISELLE</t>
   </si>
   <si>
-    <t>MONSERRATH YARETZY</t>
-  </si>
-  <si>
-    <t>EVELYN IVETH</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>ATENEA</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
   </si>
 </sst>
 </file>
@@ -1017,16 +909,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1043,16 +935,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1069,16 +961,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>70.83</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1095,16 +987,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>69.44</v>
+        <v>83.33</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1121,16 +1013,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>72.73</v>
+        <v>93.94</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1147,16 +1039,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>71.88</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1166,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1198,22 +1090,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920035</v>
+        <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1221,22 +1113,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920237</v>
+        <v>20330051920173</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1244,22 +1136,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920354</v>
+        <v>20330051920174</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1267,16 +1159,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920173</v>
+        <v>20330051920388</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1286,305 +1178,6 @@
       </c>
       <c r="G5">
         <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920393</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920183</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920111</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920285</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920286</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920293</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920310</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920312</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920233</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920345</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920158</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920044</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920365</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,6 @@
     <t>ARROYO</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
     <t>NAMORADO</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -107,9 +101,6 @@
   </si>
   <si>
     <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
   </si>
   <si>
     <t>LUZ ESTRELLA</t>
@@ -1058,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1096,10 +1087,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1113,16 +1104,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920173</v>
+        <v>20330051920174</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1136,16 +1127,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920174</v>
+        <v>20330051920388</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1154,29 +1145,6 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920388</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
         <v>2</v>
       </c>
     </row>
